--- a/data/outputSpecialityRpt/File1/RPT_RPT9853920998378DH_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT9853920998378DH_outputSpecialityRpt.xlsx
@@ -853,75 +853,75 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>1.760493157991951</v>
+        <v>12.60345975547964</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>1.751821308668415</v>
+        <v>13.32613157366968</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>1.7498650498326</v>
+        <v>9.100929288449654</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>1.735824488395584</v>
+        <v>6.573069012630077</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>1.719271231501962</v>
+        <v>6.574550068323458</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$13021.472050219514</t>
+          <t>$293339.92476993497</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$13554.145449854293</t>
+          <t>$312626.72030937625</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$14164.620088411306</t>
+          <t>$215319.24770050627</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$14727.941600881039</t>
+          <t>$156870.93216481223</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$15290.31763977193</t>
+          <t>$158199.42825647737</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,75 +993,75 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>58406003204</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>0</v>
+        <v>1.760493157991951</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
+        <v>1.751821308668415</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>0</v>
+        <v>1.7498650498326</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>0</v>
+        <v>1.735824488395584</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>0</v>
+        <v>1.719271231501962</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$88102.078125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$13021.472050219514</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$13554.145449854293</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$14164.620088411304</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$14727.941600881039</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$15290.31763977193</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
@@ -1133,75 +1133,75 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>50881001060</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>2.406472024668733</v>
+        <v>1.145769068679967</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>2.266551844799974</v>
+        <v>1.211466506697243</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>2.063369018015644</v>
+        <v>0.8273572080408778</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>1.856316765126961</v>
+        <v>0.5975517284209161</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>1.667495229339482</v>
+        <v>0.5976863698475872</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$21120.0</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$17338.871435571953</t>
+          <t>$24444.99373082791</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$17137.617721157803</t>
+          <t>$26052.22669244802</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$16335.078994802157</t>
+          <t>$17943.270641708856</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$15351.580499149868</t>
+          <t>$13072.577680401022</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$14405.299126549819</t>
+          <t>$13183.285688039778</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1273,75 +1273,75 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>0</v>
+        <v>3.262890389157498</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>0.2679116480682265</v>
+        <v>3.351683426294193</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>1.22851145635294</v>
+        <v>3.461752815092992</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>1.208359076910113</v>
+        <v>3.541101334306325</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>1.115243177454448</v>
+        <v>3.619355468158481</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$8098.643124906524</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>$772.7002693311211</t>
+          <t>$8736.92244599938</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$3741.627426548308</t>
+          <t>$9482.258057426268</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$3869.5916526698275</t>
+          <t>$10194.7446909864</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$3755.1431996238916</t>
+          <t>$10946.592129660765</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1413,75 +1413,75 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I19" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>3.262890389157499</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>3.351683426294193</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>3.461752815092992</v>
+        <v>0.4557053247637816</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>3.541101334306324</v>
+        <v>0.7512086931083873</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>3.619355468158481</v>
+        <v>0.8219711606794262</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$8098.643124906524</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$8736.92244599938</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$9482.258057426268</t>
+          <t>$8882.997139011652</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$10194.7446909864</t>
+          <t>$14756.3929534515</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$10946.592129660765</t>
+          <t>$16271.229649127677</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,75 +1553,75 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>3.270459821082147</v>
+        <v>0</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>3.414304880822506</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>3.564453883187485</v>
+        <v>5.012758572401599</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>3.713591846412171</v>
+        <v>8.26329562419226</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>3.865858214614326</v>
+        <v>9.04168276747369</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$53249.94638023091</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$58727.18647601642</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$64802.379225774144</t>
+          <t>$106595.96566813982</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$71376.49718839515</t>
+          <t>$177076.71544141797</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$78515.88124973142</t>
+          <t>$195254.75578953212</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>49702022813</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1717,51 +1717,51 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>0.1283452770043931</v>
+        <v>1.71040747665798</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>0.04260280017016599</v>
+        <v>1.291600151078349</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>0.03873219153964232</v>
+        <v>0.1750658429371191</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>0.03494223177963597</v>
+        <v>0.05299435717761748</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>0.03149776889449559</v>
+        <v>0.01734302152851921</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$5580.3798828125</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$1027.840422301081</t>
+          <t>$5173.784170230569</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$358.1171701345812</t>
+          <t>$4141.4246125965155</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$341.1532700608159</t>
+          <t>$593.220133919114</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$321.82350838064673</t>
+          <t>$189.00133634542235</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$303.1963649712163</t>
+          <t>$65.0681124501459</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>50881001060</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1857,51 +1857,51 @@
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>1.145769068679967</v>
+        <v>1.217540853336299</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>1.211466506697243</v>
+        <v>1.215554285764353</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>0.8273572080408778</v>
+        <v>1.2125838768611</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>0.597551728420916</v>
+        <v>1.206191964056825</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>0.5976863698475872</v>
+        <v>1.198868791411285</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>$21120.0</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$24444.99373082791</t>
+          <t>$10009.562061645272</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$26052.22669244802</t>
+          <t>$10455.839337862883</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$17943.270641708856</t>
+          <t>$10920.5697443441</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$13072.577680401022</t>
+          <t>$11397.7411812139</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$13183.285688039778</t>
+          <t>$11880.378673633782</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>0</v>
+        <v>1.087630129719166</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>0</v>
+        <v>1.117227808764731</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>5.012758572401599</v>
+        <v>1.153917605030997</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>8.26329562419226</v>
+        <v>1.180367111435442</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>9.04168276747369</v>
+        <v>1.206451822719494</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2678.388220417691</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2947.8891302253996</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$106595.96566813985</t>
+          <t>$3256.2789291184613</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$177076.71544141797</t>
+          <t>$3555.76712135847</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$195254.75578953212</t>
+          <t>$3877.778688032019</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>49702022813</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>TIVICAY</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2128,60 +2128,60 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I24" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1.71040747665798</v>
+        <v>2.406472024668733</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1.291600151078349</v>
+        <v>2.266551844799974</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>0.1750658429371191</v>
+        <v>2.063369018015644</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>0.05299435717761747</v>
+        <v>1.856316765126961</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>0.01734302152851921</v>
+        <v>1.667495229339482</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$5580.3798828125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$5173.784170230569</t>
+          <t>$17338.871435571953</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$4141.4246125965155</t>
+          <t>$17137.617721157803</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$593.220133919114</t>
+          <t>$16335.078994802154</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$189.00133634542235</t>
+          <t>$15351.580499149868</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$65.0681124501459</t>
+          <t>$14405.299126549819</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,75 +2253,75 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>1.2175408533363</v>
+        <v>0</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>1.215554285764353</v>
+        <v>0.2679116480682265</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>1.2125838768611</v>
+        <v>1.22851145635294</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>1.206191964056825</v>
+        <v>1.208359076910113</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>1.198868791411285</v>
+        <v>1.115243177454448</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$10009.562061645272</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$10455.839337862883</t>
+          <t>$772.7002693311211</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$10920.5697443441</t>
+          <t>$3741.627426548307</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$11397.7411812139</t>
+          <t>$3869.5916526698275</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$11880.378673633782</t>
+          <t>$3755.1431996238916</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2417,51 +2417,51 @@
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>12.60345975547964</v>
+        <v>3.270459821082147</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>13.32613157366968</v>
+        <v>3.414304880822506</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>9.100929288449654</v>
+        <v>3.564453883187485</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>6.573069012630075</v>
+        <v>3.713591846412171</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>6.574550068323458</v>
+        <v>3.865858214614326</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$293339.92476993497</t>
+          <t>$53249.94638023091</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$312626.72030937625</t>
+          <t>$58727.18647601642</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$215319.24770050627</t>
+          <t>$64802.379225774144</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$156870.93216481223</t>
+          <t>$71376.49718839515</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$158199.42825647737</t>
+          <t>$78515.88124973142</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>NEWGENERICS00069068803</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -2560,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0</v>
+        <v>1.222738880719772</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>0</v>
+        <v>2.640156318335907</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>0.4557053247637816</v>
+        <v>2.959897437238521</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>0.7512086931083873</v>
+        <v>3.143673200569508</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>0.8219711606794262</v>
+        <v>3.305381624808611</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
@@ -2581,27 +2581,27 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$67348.56633983331</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$149146.43356543517</t>
         </is>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$8882.997139011653</t>
+          <t>$171493.82721876886</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$14756.3929534515</t>
+          <t>$186809.01094559912</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$16271.229649127677</t>
+          <t>$201451.5601484315</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>58406003204</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2697,51 +2697,51 @@
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>3.344690872988271</v>
+        <v>0</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>2.163073447707928</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>2.155524831820069</v>
+        <v>0</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>2.24892283992239</v>
+        <v>0</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>2.372877999300333</v>
+        <v>0</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$88102.078125</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$204765.32304051833</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$135849.08048141183</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$138949.82176793405</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$148833.63919766038</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$161142.81783087307</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00069068803</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC IBRANCE</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -2828,60 +2828,60 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>1.222738880719772</v>
+        <v>3.34469087298827</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>2.640156318335907</v>
+        <v>2.163073447707928</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>2.959897437238521</v>
+        <v>2.155524831820069</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>3.143673200569508</v>
+        <v>2.248922839922391</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>3.305381624808611</v>
+        <v>2.372877999300333</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$67348.56633983331</t>
+          <t>$204765.32304051833</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$149146.43356543517</t>
+          <t>$135849.08048141183</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$171493.8272187689</t>
+          <t>$138949.82176793405</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$186809.01094559912</t>
+          <t>$148833.63919766038</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$201451.5601484315</t>
+          <t>$161142.81783087307</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2977,51 +2977,51 @@
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.087630129719166</v>
+        <v>0.128345277004393</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1.117227808764731</v>
+        <v>0.04260280017016599</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>1.153917605030997</v>
+        <v>0.03873219153964232</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>1.180367111435441</v>
+        <v>0.03494223177963598</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1.206451822719494</v>
+        <v>0.03149776889449559</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$2678.388220417691</t>
+          <t>$1027.840422301081</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$2947.8891302253996</t>
+          <t>$358.1171701345812</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$3256.2789291184613</t>
+          <t>$341.1532700608159</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$3555.76712135847</t>
+          <t>$321.82350838064673</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$3877.778688032019</t>
+          <t>$303.1963649712163</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
